--- a/lg-com-status-dashboard/신호등data-0801.xlsx
+++ b/lg-com-status-dashboard/신호등data-0801.xlsx
@@ -6339,7 +6339,7 @@
     <t>[WPL] Publishing Approve</t>
   </si>
   <si>
-    <t>WMO PLP FAQ</t>
+    <t>MWO PLP FAQ</t>
   </si>
   <si>
     <t>https://www.lg.com/br/micro-ondas/micro-ondas-grill/
@@ -55877,7 +55877,7 @@
       <c r="J552" s="14" t="s">
         <v>1087</v>
       </c>
-      <c r="K552" s="14" t="s">
+      <c r="K552" s="133" t="s">
         <v>1365</v>
       </c>
       <c r="L552" s="102">
@@ -55973,7 +55973,7 @@
       <c r="J553" s="14" t="s">
         <v>1087</v>
       </c>
-      <c r="K553" s="14" t="s">
+      <c r="K553" s="133" t="s">
         <v>1365</v>
       </c>
       <c r="L553" s="102">
@@ -56055,7 +56055,7 @@
       <c r="J554" s="14" t="s">
         <v>1087</v>
       </c>
-      <c r="K554" s="14" t="s">
+      <c r="K554" s="133" t="s">
         <v>1365</v>
       </c>
       <c r="L554" s="102">
@@ -56137,7 +56137,7 @@
       <c r="J555" s="14" t="s">
         <v>1087</v>
       </c>
-      <c r="K555" s="14" t="s">
+      <c r="K555" s="133" t="s">
         <v>1365</v>
       </c>
       <c r="L555" s="102">
@@ -56211,7 +56211,7 @@
       <c r="J556" s="14" t="s">
         <v>1087</v>
       </c>
-      <c r="K556" s="14" t="s">
+      <c r="K556" s="133" t="s">
         <v>1365</v>
       </c>
       <c r="L556" s="102">
@@ -56285,7 +56285,7 @@
       <c r="J557" s="14" t="s">
         <v>1087</v>
       </c>
-      <c r="K557" s="14" t="s">
+      <c r="K557" s="133" t="s">
         <v>1365</v>
       </c>
       <c r="L557" s="102">
@@ -56359,7 +56359,7 @@
       <c r="J558" s="14" t="s">
         <v>1087</v>
       </c>
-      <c r="K558" s="14" t="s">
+      <c r="K558" s="133" t="s">
         <v>1365</v>
       </c>
       <c r="L558" s="102">
@@ -56433,7 +56433,7 @@
       <c r="J559" s="14" t="s">
         <v>1087</v>
       </c>
-      <c r="K559" s="14" t="s">
+      <c r="K559" s="133" t="s">
         <v>1365</v>
       </c>
       <c r="L559" s="102">
@@ -56507,7 +56507,7 @@
       <c r="J560" s="14" t="s">
         <v>1087</v>
       </c>
-      <c r="K560" s="14" t="s">
+      <c r="K560" s="133" t="s">
         <v>1365</v>
       </c>
       <c r="L560" s="102">
@@ -56569,7 +56569,7 @@
       <c r="J561" s="14" t="s">
         <v>1087</v>
       </c>
-      <c r="K561" s="14" t="s">
+      <c r="K561" s="133" t="s">
         <v>1365</v>
       </c>
       <c r="L561" s="102">
@@ -56649,7 +56649,7 @@
       <c r="J562" s="14" t="s">
         <v>1087</v>
       </c>
-      <c r="K562" s="14" t="s">
+      <c r="K562" s="133" t="s">
         <v>1365</v>
       </c>
       <c r="L562" s="102">
@@ -56729,7 +56729,7 @@
       <c r="J563" s="14" t="s">
         <v>1087</v>
       </c>
-      <c r="K563" s="14" t="s">
+      <c r="K563" s="133" t="s">
         <v>1365</v>
       </c>
       <c r="L563" s="102">
@@ -56803,7 +56803,7 @@
       <c r="J564" s="14" t="s">
         <v>1087</v>
       </c>
-      <c r="K564" s="14" t="s">
+      <c r="K564" s="133" t="s">
         <v>1365</v>
       </c>
       <c r="L564" s="102">
@@ -56877,7 +56877,7 @@
       <c r="J565" s="14" t="s">
         <v>1087</v>
       </c>
-      <c r="K565" s="14" t="s">
+      <c r="K565" s="133" t="s">
         <v>1365</v>
       </c>
       <c r="L565" s="102">
@@ -56957,7 +56957,7 @@
       <c r="J566" s="14" t="s">
         <v>1087</v>
       </c>
-      <c r="K566" s="14" t="s">
+      <c r="K566" s="133" t="s">
         <v>1365</v>
       </c>
       <c r="L566" s="102">

--- a/lg-com-status-dashboard/신호등data-0801.xlsx
+++ b/lg-com-status-dashboard/신호등data-0801.xlsx
@@ -5,13 +5,15 @@
   <sheets>
     <sheet state="visible" name="data" sheetId="1" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">data!$A$1:$Z$566</definedName>
+  </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8342" uniqueCount="1393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8343" uniqueCount="1394">
   <si>
     <t>Region</t>
   </si>
@@ -5344,6 +5346,9 @@
   </si>
   <si>
     <t>WR2262888YZ</t>
+  </si>
+  <si>
+    <t>https://www.lg.com/th/ice-solution/</t>
   </si>
   <si>
     <t>Hi,
@@ -47639,13 +47644,17 @@
       <c r="N450" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="O450" s="14"/>
-      <c r="P450" s="14"/>
+      <c r="O450" s="114" t="s">
+        <v>1160</v>
+      </c>
+      <c r="P450" s="116">
+        <v>46230.0</v>
+      </c>
       <c r="Q450" s="115">
         <v>46092.0</v>
       </c>
       <c r="R450" s="133" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="S450" s="113">
         <v>46149.774664351855</v>
@@ -47704,7 +47713,7 @@
         <v>46093.80944444444</v>
       </c>
       <c r="E451" s="110" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="F451" s="108">
         <v>46156.541666666664</v>
@@ -47734,7 +47743,7 @@
         <v>46157.82456018519</v>
       </c>
       <c r="O451" s="128" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="P451" s="129">
         <v>46182.0</v>
@@ -47743,7 +47752,7 @@
         <v>46092.0</v>
       </c>
       <c r="R451" s="14" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="S451" s="15">
         <v>46156.80899305556</v>
@@ -47800,7 +47809,7 @@
         <v>46093.809699074074</v>
       </c>
       <c r="E452" s="110" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="F452" s="108">
         <v>46139.541666666664</v>
@@ -47830,7 +47839,7 @@
         <v>46132.713125</v>
       </c>
       <c r="O452" s="118" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="P452" s="15">
         <v>46133.94578703704</v>
@@ -47900,7 +47909,7 @@
         <v>46093.81144675926</v>
       </c>
       <c r="E453" s="110" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="F453" s="108">
         <v>46156.541666666664</v>
@@ -47930,7 +47939,7 @@
         <v>46156.653275462966</v>
       </c>
       <c r="O453" s="118" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="P453" s="15">
         <v>46160.69336805555</v>
@@ -48000,7 +48009,7 @@
         <v>46132.007314814815</v>
       </c>
       <c r="E454" s="8" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="F454" s="6">
         <v>46199.541666666664</v>
@@ -48086,7 +48095,7 @@
         <v>46132.007314814815</v>
       </c>
       <c r="E455" s="8" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="F455" s="6">
         <v>46199.541666666664</v>
@@ -48198,7 +48207,7 @@
         <v>161</v>
       </c>
       <c r="O456" s="53" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="P456" s="51" t="s">
         <v>165</v>
@@ -48286,7 +48295,7 @@
         <v>161</v>
       </c>
       <c r="O457" s="53" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="P457" s="51" t="s">
         <v>165</v>
@@ -48342,13 +48351,13 @@
         <v>50</v>
       </c>
       <c r="C458" s="51" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="D458" s="51" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="E458" s="55" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="F458" s="51" t="s">
         <v>174</v>
@@ -48375,10 +48384,10 @@
         <v>890</v>
       </c>
       <c r="N458" s="51" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="O458" s="53" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="P458" s="52">
         <v>46082.30763888889</v>
@@ -48390,19 +48399,19 @@
         <v>296</v>
       </c>
       <c r="S458" s="51" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="T458" s="52">
         <v>46082.31041666667</v>
       </c>
       <c r="U458" s="51" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="V458" s="51" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="W458" s="51" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="X458" s="55"/>
       <c r="Y458" s="56" t="s">
@@ -48446,7 +48455,7 @@
         <v>222</v>
       </c>
       <c r="E459" s="55" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="F459" s="51" t="s">
         <v>174</v>
@@ -48473,10 +48482,10 @@
         <v>176</v>
       </c>
       <c r="N459" s="51" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O459" s="53" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="P459" s="51" t="s">
         <v>190</v>
@@ -48485,7 +48494,7 @@
         <v>148</v>
       </c>
       <c r="R459" s="55" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="S459" s="51" t="s">
         <v>219</v>
@@ -48494,16 +48503,16 @@
         <v>193</v>
       </c>
       <c r="U459" s="51" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="V459" s="51" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="W459" s="51" t="s">
         <v>219</v>
       </c>
       <c r="X459" s="51" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="Y459" s="56" t="s">
         <v>150</v>
@@ -48546,7 +48555,7 @@
         <v>46132.00827546296</v>
       </c>
       <c r="E460" s="8" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="F460" s="6">
         <v>46231.541666666664</v>
@@ -48628,7 +48637,7 @@
         <v>46132.00827546296</v>
       </c>
       <c r="E461" s="8" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="F461" s="6">
         <v>46231.541666666664</v>
@@ -48710,7 +48719,7 @@
         <v>46132.00833333333</v>
       </c>
       <c r="E462" s="8" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="F462" s="6">
         <v>46231.541666666664</v>
@@ -48792,7 +48801,7 @@
         <v>46132.00833333333</v>
       </c>
       <c r="E463" s="8" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="F463" s="6">
         <v>46231.541666666664</v>
@@ -48868,13 +48877,13 @@
         <v>249</v>
       </c>
       <c r="C464" s="51" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="D464" s="51" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="E464" s="55" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="F464" s="69">
         <v>46266.583333333336</v>
@@ -48904,7 +48913,7 @@
         <v>46266.291666666664</v>
       </c>
       <c r="O464" s="53" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="P464" s="52">
         <v>46296.04861111111</v>
@@ -48920,13 +48929,13 @@
         <v>46296.06180555555</v>
       </c>
       <c r="U464" s="51" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="V464" s="51" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="W464" s="51" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="X464" s="55"/>
       <c r="Y464" s="56" t="s">
@@ -49000,7 +49009,7 @@
         <v>46266.291666666664</v>
       </c>
       <c r="O465" s="53" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="P465" s="52">
         <v>46296.04861111111</v>
@@ -49054,13 +49063,13 @@
         <v>61</v>
       </c>
       <c r="C466" s="51" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="D466" s="51" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="E466" s="55" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="F466" s="51" t="s">
         <v>293</v>
@@ -49090,17 +49099,17 @@
         <v>282</v>
       </c>
       <c r="O466" s="53" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="P466" s="51" t="s">
         <v>284</v>
       </c>
       <c r="Q466" s="68"/>
       <c r="R466" s="55" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="S466" s="51" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="T466" s="52">
         <v>46082.30625</v>
@@ -49109,10 +49118,10 @@
         <v>927</v>
       </c>
       <c r="V466" s="51" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="W466" s="51" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="X466" s="55"/>
       <c r="Y466" s="56" t="s">
@@ -49150,13 +49159,13 @@
         <v>61</v>
       </c>
       <c r="C467" s="51" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="D467" s="51" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="E467" s="55" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="F467" s="51" t="s">
         <v>174</v>
@@ -49186,17 +49195,17 @@
         <v>934</v>
       </c>
       <c r="O467" s="53" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="P467" s="51" t="s">
         <v>284</v>
       </c>
       <c r="Q467" s="68"/>
       <c r="R467" s="55" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="S467" s="51" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="T467" s="52">
         <v>46082.31041666667</v>
@@ -49205,10 +49214,10 @@
         <v>894</v>
       </c>
       <c r="V467" s="51" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="W467" s="51" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="X467" s="55"/>
       <c r="Y467" s="56" t="s">
@@ -49252,7 +49261,7 @@
         <v>46132.00821759259</v>
       </c>
       <c r="E468" s="8" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="F468" s="6">
         <v>46231.541666666664</v>
@@ -49282,7 +49291,7 @@
         <v>32</v>
       </c>
       <c r="O468" s="70" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="P468" s="17"/>
       <c r="Q468" s="62">
@@ -49336,7 +49345,7 @@
         <v>46132.00821759259</v>
       </c>
       <c r="E469" s="8" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="F469" s="6">
         <v>46231.541666666664</v>
@@ -49366,7 +49375,7 @@
         <v>32</v>
       </c>
       <c r="O469" s="70" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="P469" s="17"/>
       <c r="Q469" s="62">
@@ -49450,10 +49459,10 @@
         <v>32</v>
       </c>
       <c r="O470" s="53" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="P470" s="51" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="Q470" s="68"/>
       <c r="R470" s="55" t="s">
@@ -49546,10 +49555,10 @@
         <v>32</v>
       </c>
       <c r="O471" s="53" t="s">
+        <v>1223</v>
+      </c>
+      <c r="P471" s="51" t="s">
         <v>1222</v>
-      </c>
-      <c r="P471" s="51" t="s">
-        <v>1221</v>
       </c>
       <c r="Q471" s="68"/>
       <c r="R471" s="55" t="s">
@@ -49612,7 +49621,7 @@
         <v>46132.00846064815</v>
       </c>
       <c r="E472" s="8" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="F472" s="6">
         <v>46146.541666666664</v>
@@ -49698,7 +49707,7 @@
         <v>46132.00846064815</v>
       </c>
       <c r="E473" s="8" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="F473" s="6">
         <v>46146.541666666664</v>
@@ -49784,7 +49793,7 @@
         <v>45973.927777777775</v>
       </c>
       <c r="E474" s="55" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="F474" s="51" t="s">
         <v>384</v>
@@ -49793,7 +49802,7 @@
         <v>175</v>
       </c>
       <c r="H474" s="51" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="I474" s="55" t="s">
         <v>29</v>
@@ -49808,13 +49817,13 @@
         <v>1.0</v>
       </c>
       <c r="M474" s="51" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="N474" s="51" t="s">
         <v>425</v>
       </c>
       <c r="O474" s="53" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="P474" s="51" t="s">
         <v>418</v>
@@ -49824,22 +49833,22 @@
         <v>440</v>
       </c>
       <c r="S474" s="51" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="T474" s="51" t="s">
         <v>419</v>
       </c>
       <c r="U474" s="51" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="V474" s="51" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="W474" s="51" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="X474" s="51" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="Y474" s="56" t="s">
         <v>150</v>
@@ -49882,7 +49891,7 @@
         <v>45973.927777777775</v>
       </c>
       <c r="E475" s="55" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="F475" s="51" t="s">
         <v>384</v>
@@ -49891,7 +49900,7 @@
         <v>175</v>
       </c>
       <c r="H475" s="51" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="I475" s="55" t="s">
         <v>29</v>
@@ -49906,38 +49915,38 @@
         <v>1.0</v>
       </c>
       <c r="M475" s="51" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="N475" s="51" t="s">
         <v>425</v>
       </c>
       <c r="O475" s="53" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="P475" s="51" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="Q475" s="68"/>
       <c r="R475" s="55" t="s">
         <v>408</v>
       </c>
       <c r="S475" s="51" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="T475" s="51" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="U475" s="51" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="V475" s="51" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="W475" s="51" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="X475" s="51" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="Y475" s="56" t="s">
         <v>150</v>
@@ -49980,7 +49989,7 @@
         <v>45728.893055555556</v>
       </c>
       <c r="E476" s="55" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="F476" s="69">
         <v>45942.583333333336</v>
@@ -50010,7 +50019,7 @@
         <v>465</v>
       </c>
       <c r="O476" s="53" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="P476" s="51" t="s">
         <v>407</v>
@@ -50078,7 +50087,7 @@
         <v>45728.89375</v>
       </c>
       <c r="E477" s="55" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="F477" s="69">
         <v>45973.583333333336</v>
@@ -50108,7 +50117,7 @@
         <v>465</v>
       </c>
       <c r="O477" s="53" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="P477" s="51" t="s">
         <v>407</v>
@@ -50118,7 +50127,7 @@
         <v>435</v>
       </c>
       <c r="S477" s="51" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="T477" s="51" t="s">
         <v>971</v>
@@ -50544,7 +50553,7 @@
         <v>46132.00803240741</v>
       </c>
       <c r="E482" s="8" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="F482" s="6">
         <v>46132.541666666664</v>
@@ -50634,7 +50643,7 @@
         <v>46132.00803240741</v>
       </c>
       <c r="E483" s="8" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="F483" s="6">
         <v>46132.541666666664</v>
@@ -50724,7 +50733,7 @@
         <v>46132.00809027778</v>
       </c>
       <c r="E484" s="8" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="F484" s="6">
         <v>46193.541666666664</v>
@@ -50812,7 +50821,7 @@
         <v>46132.00809027778</v>
       </c>
       <c r="E485" s="8" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="F485" s="6">
         <v>46193.541666666664</v>
@@ -50900,7 +50909,7 @@
         <v>46132.00840277778</v>
       </c>
       <c r="E486" s="77" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="F486" s="29">
         <v>46132.541666666664</v>
@@ -50982,7 +50991,7 @@
         <v>46132.00840277778</v>
       </c>
       <c r="E487" s="77" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="F487" s="29">
         <v>46132.541666666664</v>
@@ -51064,7 +51073,7 @@
         <v>46132.00814814815</v>
       </c>
       <c r="E488" s="8" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="F488" s="6">
         <v>46234.541666666664</v>
@@ -51152,7 +51161,7 @@
         <v>46132.00814814815</v>
       </c>
       <c r="E489" s="8" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="F489" s="6">
         <v>46234.541666666664</v>
@@ -51240,7 +51249,7 @@
         <v>46132.010150462964</v>
       </c>
       <c r="E490" s="8" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="F490" s="6">
         <v>46136.541666666664</v>
@@ -51330,7 +51339,7 @@
         <v>46132.010150462964</v>
       </c>
       <c r="E491" s="8" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="F491" s="6">
         <v>46136.541666666664</v>
@@ -51420,10 +51429,10 @@
         <v>268</v>
       </c>
       <c r="E492" s="11" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="F492" s="10" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="G492" s="10" t="s">
         <v>175</v>
@@ -51453,7 +51462,7 @@
       <c r="P492" s="17"/>
       <c r="Q492" s="25"/>
       <c r="R492" s="11" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="S492" s="67">
         <v>46267.99513888889</v>
@@ -51463,11 +51472,11 @@
       </c>
       <c r="U492" s="17"/>
       <c r="V492" s="10" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="W492" s="17"/>
       <c r="X492" s="10" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="Y492" s="18" t="s">
         <v>150</v>
@@ -51516,7 +51525,7 @@
         <v>46269.0</v>
       </c>
       <c r="G493" s="23" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="H493" s="23" t="s">
         <v>67</v>
@@ -51549,7 +51558,7 @@
       <c r="V493" s="17"/>
       <c r="W493" s="17"/>
       <c r="X493" s="23" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="Y493" s="18" t="s">
         <v>35</v>
@@ -51592,7 +51601,7 @@
         <v>46132.00996527778</v>
       </c>
       <c r="E494" s="77" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="F494" s="29">
         <v>46132.541666666664</v>
@@ -51674,7 +51683,7 @@
         <v>46132.00996527778</v>
       </c>
       <c r="E495" s="77" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="F495" s="29">
         <v>46132.541666666664</v>
@@ -51756,7 +51765,7 @@
         <v>46132.010625</v>
       </c>
       <c r="E496" s="8" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="F496" s="6">
         <v>46132.541666666664</v>
@@ -51842,7 +51851,7 @@
         <v>46132.010625</v>
       </c>
       <c r="E497" s="8" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="F497" s="6">
         <v>46132.541666666664</v>
@@ -51928,7 +51937,7 @@
         <v>557</v>
       </c>
       <c r="E498" s="55" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="F498" s="51" t="s">
         <v>214</v>
@@ -51955,10 +51964,10 @@
         <v>1006</v>
       </c>
       <c r="N498" s="51" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="O498" s="53" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="P498" s="52">
         <v>46082.30347222222</v>
@@ -51968,7 +51977,7 @@
         <v>296</v>
       </c>
       <c r="S498" s="51" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="T498" s="52">
         <v>46082.30625</v>
@@ -51980,7 +51989,7 @@
         <v>299</v>
       </c>
       <c r="W498" s="51" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="X498" s="55"/>
       <c r="Y498" s="56" t="s">
@@ -52018,13 +52027,13 @@
         <v>86</v>
       </c>
       <c r="C499" s="51" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="D499" s="51" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="E499" s="55" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="F499" s="69">
         <v>46143.583333333336</v>
@@ -52054,27 +52063,27 @@
         <v>32</v>
       </c>
       <c r="O499" s="53" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="P499" s="52">
         <v>46082.30763888889</v>
       </c>
       <c r="Q499" s="68"/>
       <c r="R499" s="55" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="S499" s="51" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="T499" s="55"/>
       <c r="U499" s="51" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="V499" s="51" t="s">
+        <v>1275</v>
+      </c>
+      <c r="W499" s="51" t="s">
         <v>1274</v>
-      </c>
-      <c r="W499" s="51" t="s">
-        <v>1273</v>
       </c>
       <c r="X499" s="52">
         <v>46082.32916666667</v>
@@ -52120,7 +52129,7 @@
         <v>46132.010567129626</v>
       </c>
       <c r="E500" s="77" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="F500" s="29">
         <v>46132.541666666664</v>
@@ -52202,7 +52211,7 @@
         <v>46132.010567129626</v>
       </c>
       <c r="E501" s="77" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="F501" s="29">
         <v>46132.541666666664</v>
@@ -52284,7 +52293,7 @@
         <v>46132.01050925926</v>
       </c>
       <c r="E502" s="77" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="F502" s="29">
         <v>46132.541666666664</v>
@@ -52366,7 +52375,7 @@
         <v>46132.01050925926</v>
       </c>
       <c r="E503" s="77" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="F503" s="29">
         <v>46132.541666666664</v>
@@ -52478,7 +52487,7 @@
         <v>32</v>
       </c>
       <c r="O504" s="40" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="P504" s="17"/>
       <c r="Q504" s="10" t="s">
@@ -52572,7 +52581,7 @@
         <v>32</v>
       </c>
       <c r="O505" s="40" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="P505" s="17"/>
       <c r="Q505" s="10" t="s">
@@ -52636,7 +52645,7 @@
         <v>645</v>
       </c>
       <c r="E506" s="11" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="F506" s="10" t="s">
         <v>293</v>
@@ -52669,20 +52678,20 @@
       <c r="P506" s="17"/>
       <c r="Q506" s="25"/>
       <c r="R506" s="11" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="S506" s="10" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="T506" s="17"/>
       <c r="U506" s="10" t="s">
+        <v>1285</v>
+      </c>
+      <c r="V506" s="10" t="s">
+        <v>1286</v>
+      </c>
+      <c r="W506" s="10" t="s">
         <v>1284</v>
-      </c>
-      <c r="V506" s="10" t="s">
-        <v>1285</v>
-      </c>
-      <c r="W506" s="10" t="s">
-        <v>1283</v>
       </c>
       <c r="X506" s="71" t="s">
         <v>662</v>
@@ -52702,13 +52711,13 @@
         <v>634</v>
       </c>
       <c r="C507" s="10" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="D507" s="10" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="E507" s="11" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="F507" s="29">
         <v>46054.583333333336</v>
@@ -52741,20 +52750,20 @@
       <c r="P507" s="17"/>
       <c r="Q507" s="25"/>
       <c r="R507" s="11" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="S507" s="10" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="T507" s="17"/>
       <c r="U507" s="10" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="V507" s="10" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="W507" s="10" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="X507" s="78">
         <v>46054.19236111111</v>
@@ -52780,16 +52789,16 @@
         <v>691</v>
       </c>
       <c r="E508" s="55" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="F508" s="51" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="G508" s="51" t="s">
         <v>175</v>
       </c>
       <c r="H508" s="51" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="I508" s="55" t="s">
         <v>29</v>
@@ -52804,16 +52813,16 @@
         <v>1.0</v>
       </c>
       <c r="M508" s="51" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="N508" s="51" t="s">
         <v>694</v>
       </c>
       <c r="O508" s="53" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="P508" s="51" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="Q508" s="68"/>
       <c r="R508" s="55" t="s">
@@ -52823,19 +52832,19 @@
         <v>425</v>
       </c>
       <c r="T508" s="51" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="U508" s="51" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="V508" s="51" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="W508" s="51" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="X508" s="51" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="Y508" s="56" t="s">
         <v>150</v>
@@ -52858,16 +52867,16 @@
         <v>691</v>
       </c>
       <c r="E509" s="55" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="F509" s="51" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="G509" s="51" t="s">
         <v>175</v>
       </c>
       <c r="H509" s="51" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="I509" s="55" t="s">
         <v>29</v>
@@ -52882,16 +52891,16 @@
         <v>1.0</v>
       </c>
       <c r="M509" s="51" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="N509" s="51" t="s">
         <v>694</v>
       </c>
       <c r="O509" s="53" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="P509" s="51" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="Q509" s="68"/>
       <c r="R509" s="55" t="s">
@@ -52901,19 +52910,19 @@
         <v>425</v>
       </c>
       <c r="T509" s="51" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="U509" s="51" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="V509" s="51" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="W509" s="51" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="X509" s="51" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="Y509" s="56" t="s">
         <v>150</v>
@@ -52936,7 +52945,7 @@
         <v>46132.0102662037</v>
       </c>
       <c r="E510" s="8" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="F510" s="6">
         <v>46199.541666666664</v>
@@ -53004,7 +53013,7 @@
         <v>46132.0102662037</v>
       </c>
       <c r="E511" s="8" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="F511" s="6">
         <v>46199.541666666664</v>
@@ -53072,7 +53081,7 @@
         <v>46132.01002314815</v>
       </c>
       <c r="E512" s="8" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="F512" s="6">
         <v>46237.541666666664</v>
@@ -53134,7 +53143,7 @@
         <v>46132.01002314815</v>
       </c>
       <c r="E513" s="8" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="F513" s="6">
         <v>46237.541666666664</v>
@@ -53196,7 +53205,7 @@
         <v>45973.92847222222</v>
       </c>
       <c r="E514" s="55" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="F514" s="51" t="s">
         <v>680</v>
@@ -53226,7 +53235,7 @@
         <v>769</v>
       </c>
       <c r="O514" s="53" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="P514" s="51" t="s">
         <v>748</v>
@@ -53245,10 +53254,10 @@
         <v>764</v>
       </c>
       <c r="V514" s="51" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="W514" s="51" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="X514" s="51" t="s">
         <v>774</v>
@@ -53274,7 +53283,7 @@
         <v>45973.92847222222</v>
       </c>
       <c r="E515" s="55" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="F515" s="51" t="s">
         <v>680</v>
@@ -53283,7 +53292,7 @@
         <v>175</v>
       </c>
       <c r="H515" s="51" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="I515" s="55" t="s">
         <v>29</v>
@@ -53298,13 +53307,13 @@
         <v>1.0</v>
       </c>
       <c r="M515" s="51" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="N515" s="51" t="s">
         <v>769</v>
       </c>
       <c r="O515" s="53" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="P515" s="51" t="s">
         <v>748</v>
@@ -53314,22 +53323,22 @@
         <v>179</v>
       </c>
       <c r="S515" s="51" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="T515" s="51" t="s">
         <v>750</v>
       </c>
       <c r="U515" s="51" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="V515" s="51" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="W515" s="51" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="X515" s="51" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="Y515" s="56" t="s">
         <v>150</v>
@@ -53380,7 +53389,7 @@
         <v>769</v>
       </c>
       <c r="O516" s="53" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="P516" s="52">
         <v>45942.89722222222</v>
@@ -53399,10 +53408,10 @@
         <v>764</v>
       </c>
       <c r="V516" s="51" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="W516" s="51" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="X516" s="51" t="s">
         <v>774</v>
@@ -53435,7 +53444,7 @@
         <v>175</v>
       </c>
       <c r="H517" s="51" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="I517" s="55" t="s">
         <v>29</v>
@@ -53456,7 +53465,7 @@
         <v>769</v>
       </c>
       <c r="O517" s="53" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="P517" s="52">
         <v>45942.89722222222</v>
@@ -53466,22 +53475,22 @@
         <v>179</v>
       </c>
       <c r="S517" s="51" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="T517" s="51" t="s">
         <v>750</v>
       </c>
       <c r="U517" s="51" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="V517" s="51" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="W517" s="51" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="X517" s="51" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="Y517" s="56" t="s">
         <v>150</v>
@@ -53504,7 +53513,7 @@
         <v>46132.01032407407</v>
       </c>
       <c r="E518" s="77" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="F518" s="29">
         <v>46148.541666666664</v>
@@ -53570,7 +53579,7 @@
         <v>46132.01032407407</v>
       </c>
       <c r="E519" s="77" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="F519" s="29">
         <v>46148.541666666664</v>
@@ -53636,7 +53645,7 @@
         <v>46114.54652777778</v>
       </c>
       <c r="E520" s="11" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="F520" s="29">
         <v>46297.583333333336</v>
@@ -53666,7 +53675,7 @@
         <v>32</v>
       </c>
       <c r="O520" s="79" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="P520" s="17"/>
       <c r="Q520" s="25"/>
@@ -53710,7 +53719,7 @@
         <v>46114.54652777778</v>
       </c>
       <c r="E521" s="11" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="F521" s="29">
         <v>46358.583333333336</v>
@@ -53740,7 +53749,7 @@
         <v>32</v>
       </c>
       <c r="O521" s="79" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="P521" s="17"/>
       <c r="Q521" s="17"/>
@@ -53812,7 +53821,7 @@
         <v>827</v>
       </c>
       <c r="O522" s="53" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="P522" s="51" t="s">
         <v>829</v>
@@ -53890,7 +53899,7 @@
         <v>827</v>
       </c>
       <c r="O523" s="75" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="P523" s="136" t="s">
         <v>829</v>
@@ -53940,7 +53949,7 @@
         <v>46132.01008101852</v>
       </c>
       <c r="E524" s="77" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="F524" s="29">
         <v>46132.541666666664</v>
@@ -54002,7 +54011,7 @@
         <v>46132.01008101852</v>
       </c>
       <c r="E525" s="77" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="F525" s="29">
         <v>46132.541666666664</v>
@@ -54092,7 +54101,7 @@
         <v>827</v>
       </c>
       <c r="O526" s="53" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="P526" s="51" t="s">
         <v>852</v>
@@ -54170,7 +54179,7 @@
         <v>827</v>
       </c>
       <c r="O527" s="53" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="P527" s="51" t="s">
         <v>852</v>
@@ -54250,7 +54259,7 @@
         <v>45942.009722222225</v>
       </c>
       <c r="O528" s="53" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="P528" s="51" t="s">
         <v>860</v>
@@ -54326,7 +54335,7 @@
         <v>45942.009722222225</v>
       </c>
       <c r="O529" s="53" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="P529" s="51" t="s">
         <v>860</v>
@@ -54402,7 +54411,7 @@
         <v>827</v>
       </c>
       <c r="O530" s="53" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="P530" s="51" t="s">
         <v>868</v>
@@ -54482,7 +54491,7 @@
         <v>827</v>
       </c>
       <c r="O531" s="75" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="P531" s="136" t="s">
         <v>868</v>
@@ -54532,7 +54541,7 @@
         <v>46132.01045138889</v>
       </c>
       <c r="E532" s="8" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="F532" s="6">
         <v>46132.541666666664</v>
@@ -54600,7 +54609,7 @@
         <v>46132.01045138889</v>
       </c>
       <c r="E533" s="8" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="F533" s="6">
         <v>46132.541666666664</v>
@@ -54683,10 +54692,10 @@
         <v>29</v>
       </c>
       <c r="J534" s="14" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="K534" s="137" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="L534" s="102">
         <v>204.0</v>
@@ -54726,7 +54735,7 @@
         <v>32</v>
       </c>
       <c r="Z534" s="138" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="535" ht="15.0" customHeight="1">
@@ -54743,7 +54752,7 @@
         <v>46156.796319444446</v>
       </c>
       <c r="E535" s="8" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="F535" s="6">
         <v>46228.541666666664</v>
@@ -54758,10 +54767,10 @@
         <v>133</v>
       </c>
       <c r="J535" s="14" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="K535" s="137" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="L535" s="102">
         <v>81.0</v>
@@ -54777,7 +54786,7 @@
         <v>46153.0</v>
       </c>
       <c r="R535" s="5" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="S535" s="6">
         <v>46226.6665162037</v>
@@ -54795,7 +54804,7 @@
         <v>32</v>
       </c>
       <c r="Z535" s="138" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="536" ht="15.0" customHeight="1">
@@ -54812,7 +54821,7 @@
         <v>46156.796331018515</v>
       </c>
       <c r="E536" s="8" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="F536" s="6">
         <v>46156.541666666664</v>
@@ -54827,10 +54836,10 @@
         <v>146</v>
       </c>
       <c r="J536" s="14" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="K536" s="137" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="L536" s="102">
         <v>370.0</v>
@@ -54846,7 +54855,7 @@
         <v>46153.0</v>
       </c>
       <c r="R536" s="5" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="S536" s="6">
         <v>46165.47635416667</v>
@@ -54862,7 +54871,7 @@
         <v>32</v>
       </c>
       <c r="Z536" s="138" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="537" ht="15.0" customHeight="1">
@@ -54879,7 +54888,7 @@
         <v>46156.79634259259</v>
       </c>
       <c r="E537" s="8" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="F537" s="6">
         <v>46156.541666666664</v>
@@ -54894,10 +54903,10 @@
         <v>146</v>
       </c>
       <c r="J537" s="14" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="K537" s="137" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="L537" s="102">
         <v>357.0</v>
@@ -54913,7 +54922,7 @@
         <v>46153.0</v>
       </c>
       <c r="R537" s="5" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="S537" s="6">
         <v>46165.635671296295</v>
@@ -54929,7 +54938,7 @@
         <v>32</v>
       </c>
       <c r="Z537" s="138" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="538" ht="15.0" customHeight="1">
@@ -54946,7 +54955,7 @@
         <v>46156.79635416667</v>
       </c>
       <c r="E538" s="8" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="F538" s="6">
         <v>46156.541666666664</v>
@@ -54961,10 +54970,10 @@
         <v>42</v>
       </c>
       <c r="J538" s="14" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="K538" s="137" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="L538" s="102">
         <v>136.0</v>
@@ -54990,7 +54999,7 @@
         <v>32</v>
       </c>
       <c r="Z538" s="138" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="539" ht="15.0" customHeight="1">
@@ -55007,7 +55016,7 @@
         <v>46156.796377314815</v>
       </c>
       <c r="E539" s="8" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="F539" s="6">
         <v>46156.541666666664</v>
@@ -55022,10 +55031,10 @@
         <v>42</v>
       </c>
       <c r="J539" s="14" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="K539" s="137" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="L539" s="102">
         <v>347.0</v>
@@ -55051,7 +55060,7 @@
         <v>32</v>
       </c>
       <c r="Z539" s="138" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="540" ht="15.0" customHeight="1">
@@ -55068,7 +55077,7 @@
         <v>46156.79646990741</v>
       </c>
       <c r="E540" s="8" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="F540" s="6">
         <v>46156.541666666664</v>
@@ -55083,10 +55092,10 @@
         <v>42</v>
       </c>
       <c r="J540" s="14" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="K540" s="137" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="L540" s="102">
         <v>386.0</v>
@@ -55112,7 +55121,7 @@
         <v>32</v>
       </c>
       <c r="Z540" s="138" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="541" ht="15.0" customHeight="1">
@@ -55129,7 +55138,7 @@
         <v>46156.79636574074</v>
       </c>
       <c r="E541" s="8" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="F541" s="6">
         <v>46156.541666666664</v>
@@ -55144,10 +55153,10 @@
         <v>42</v>
       </c>
       <c r="J541" s="14" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="K541" s="137" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="L541" s="102">
         <v>563.0</v>
@@ -55173,7 +55182,7 @@
         <v>32</v>
       </c>
       <c r="Z541" s="138" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="542" ht="15.0" customHeight="1">
@@ -55190,7 +55199,7 @@
         <v>46156.79640046296</v>
       </c>
       <c r="E542" s="8" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="F542" s="6">
         <v>46234.541666666664</v>
@@ -55205,10 +55214,10 @@
         <v>46</v>
       </c>
       <c r="J542" s="14" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="K542" s="137" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="L542" s="102">
         <v>107.0</v>
@@ -55234,7 +55243,7 @@
         <v>32</v>
       </c>
       <c r="Z542" s="138" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="543" ht="15.0" customHeight="1">
@@ -55251,7 +55260,7 @@
         <v>46156.79638888889</v>
       </c>
       <c r="E543" s="8" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="F543" s="6">
         <v>46203.541666666664</v>
@@ -55266,10 +55275,10 @@
         <v>29</v>
       </c>
       <c r="J543" s="14" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="K543" s="137" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="L543" s="102">
         <v>420.0</v>
@@ -55285,7 +55294,7 @@
         <v>46153.0</v>
       </c>
       <c r="R543" s="5" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="S543" s="6">
         <v>46188.73607638889</v>
@@ -55309,7 +55318,7 @@
         <v>32</v>
       </c>
       <c r="Z543" s="138" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="544" ht="15.0" customHeight="1">
@@ -55326,7 +55335,7 @@
         <v>46156.79641203704</v>
       </c>
       <c r="E544" s="8" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="F544" s="6">
         <v>46156.541666666664</v>
@@ -55341,10 +55350,10 @@
         <v>42</v>
       </c>
       <c r="J544" s="14" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="K544" s="137" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="L544" s="102">
         <v>429.0</v>
@@ -55370,7 +55379,7 @@
         <v>32</v>
       </c>
       <c r="Z544" s="138" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="545" ht="15.0" customHeight="1">
@@ -55387,7 +55396,7 @@
         <v>46156.796423611115</v>
       </c>
       <c r="E545" s="8" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="F545" s="6">
         <v>46156.541666666664</v>
@@ -55402,10 +55411,10 @@
         <v>42</v>
       </c>
       <c r="J545" s="14" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="K545" s="137" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="L545" s="102">
         <v>230.0</v>
@@ -55431,7 +55440,7 @@
         <v>32</v>
       </c>
       <c r="Z545" s="138" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="546" ht="15.0" customHeight="1">
@@ -55448,7 +55457,7 @@
         <v>46156.79644675926</v>
       </c>
       <c r="E546" s="8" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="F546" s="6">
         <v>46234.541666666664</v>
@@ -55463,10 +55472,10 @@
         <v>29</v>
       </c>
       <c r="J546" s="14" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="K546" s="137" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="L546" s="102">
         <v>154.0</v>
@@ -55482,7 +55491,7 @@
         <v>46153.0</v>
       </c>
       <c r="R546" s="5" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="S546" s="6">
         <v>46219.63613425926</v>
@@ -55506,7 +55515,7 @@
         <v>32</v>
       </c>
       <c r="Z546" s="138" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="547" ht="15.0" customHeight="1">
@@ -55523,7 +55532,7 @@
         <v>46156.796435185184</v>
       </c>
       <c r="E547" s="8" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="F547" s="6">
         <v>46234.541666666664</v>
@@ -55538,10 +55547,10 @@
         <v>29</v>
       </c>
       <c r="J547" s="14" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="K547" s="137" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="L547" s="102">
         <v>264.0</v>
@@ -55557,7 +55566,7 @@
         <v>46153.0</v>
       </c>
       <c r="R547" s="5" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="S547" s="6">
         <v>46219.63568287037</v>
@@ -55581,7 +55590,7 @@
         <v>32</v>
       </c>
       <c r="Z547" s="138" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="548" ht="15.0" customHeight="1">
@@ -55598,7 +55607,7 @@
         <v>46156.796481481484</v>
       </c>
       <c r="E548" s="8" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="F548" s="6">
         <v>46248.541666666664</v>
@@ -55613,10 +55622,10 @@
         <v>46</v>
       </c>
       <c r="J548" s="14" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="K548" s="137" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="L548" s="102">
         <v>203.0</v>
@@ -55632,7 +55641,7 @@
         <v>46153.0</v>
       </c>
       <c r="R548" s="5" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="S548" s="6">
         <v>46226.495300925926</v>
@@ -55646,7 +55655,7 @@
         <v>32</v>
       </c>
       <c r="Z548" s="138" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="549" ht="15.0" customHeight="1">
@@ -55663,7 +55672,7 @@
         <v>46156.79649305555</v>
       </c>
       <c r="E549" s="8" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="F549" s="6">
         <v>46156.541666666664</v>
@@ -55678,10 +55687,10 @@
         <v>42</v>
       </c>
       <c r="J549" s="14" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="K549" s="137" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="L549" s="102">
         <v>164.0</v>
@@ -55707,7 +55716,7 @@
         <v>32</v>
       </c>
       <c r="Z549" s="138" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="550" ht="15.0" customHeight="1">
@@ -55724,7 +55733,7 @@
         <v>46156.79651620371</v>
       </c>
       <c r="E550" s="8" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="F550" s="6">
         <v>46234.541666666664</v>
@@ -55739,10 +55748,10 @@
         <v>29</v>
       </c>
       <c r="J550" s="14" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="K550" s="137" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="L550" s="102">
         <v>192.0</v>
@@ -55782,7 +55791,7 @@
         <v>32</v>
       </c>
       <c r="Z550" s="138" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="551" ht="15.0" customHeight="1">
@@ -55799,7 +55808,7 @@
         <v>46156.79645833333</v>
       </c>
       <c r="E551" s="8" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="F551" s="6">
         <v>46156.541666666664</v>
@@ -55814,10 +55823,10 @@
         <v>42</v>
       </c>
       <c r="J551" s="14" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="K551" s="137" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="L551" s="102">
         <v>101.0</v>
@@ -55843,7 +55852,7 @@
         <v>32</v>
       </c>
       <c r="Z551" s="138" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="552" ht="15.0" customHeight="1">
@@ -55860,7 +55869,7 @@
         <v>46180.77123842593</v>
       </c>
       <c r="E552" s="8" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="F552" s="6">
         <v>46228.541666666664</v>
@@ -55872,13 +55881,13 @@
         <v>46223.978483796294</v>
       </c>
       <c r="I552" s="5" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="J552" s="14" t="s">
         <v>1087</v>
       </c>
       <c r="K552" s="133" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="L552" s="102">
         <v>4.0</v>
@@ -55890,7 +55899,7 @@
         <v>46223.93716435185</v>
       </c>
       <c r="O552" s="5" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="P552" s="64"/>
       <c r="Q552" s="115">
@@ -55956,7 +55965,7 @@
         <v>46180.77125</v>
       </c>
       <c r="E553" s="8" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="F553" s="6">
         <v>46176.541666666664</v>
@@ -55974,7 +55983,7 @@
         <v>1087</v>
       </c>
       <c r="K553" s="133" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="L553" s="102">
         <v>1.0</v>
@@ -56038,7 +56047,7 @@
         <v>46180.771261574075</v>
       </c>
       <c r="E554" s="8" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="F554" s="6">
         <v>46176.541666666664</v>
@@ -56056,7 +56065,7 @@
         <v>1087</v>
       </c>
       <c r="K554" s="133" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="L554" s="102">
         <v>4.0</v>
@@ -56120,7 +56129,7 @@
         <v>46180.77127314815</v>
       </c>
       <c r="E555" s="8" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="F555" s="6">
         <v>46213.541666666664</v>
@@ -56138,7 +56147,7 @@
         <v>1087</v>
       </c>
       <c r="K555" s="133" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="L555" s="102">
         <v>1.0</v>
@@ -56150,7 +56159,7 @@
         <v>32</v>
       </c>
       <c r="O555" s="12" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="P555" s="140"/>
       <c r="Q555" s="115">
@@ -56194,7 +56203,7 @@
         <v>46180.77128472222</v>
       </c>
       <c r="E556" s="8" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="F556" s="6">
         <v>46213.541666666664</v>
@@ -56212,7 +56221,7 @@
         <v>1087</v>
       </c>
       <c r="K556" s="133" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="L556" s="102">
         <v>4.0</v>
@@ -56224,7 +56233,7 @@
         <v>32</v>
       </c>
       <c r="O556" s="5" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="P556" s="140"/>
       <c r="Q556" s="115">
@@ -56268,7 +56277,7 @@
         <v>46180.7712962963</v>
       </c>
       <c r="E557" s="8" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="F557" s="6">
         <v>46234.541666666664</v>
@@ -56286,7 +56295,7 @@
         <v>1087</v>
       </c>
       <c r="K557" s="133" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="L557" s="102">
         <v>3.0</v>
@@ -56303,7 +56312,7 @@
         <v>46175.0</v>
       </c>
       <c r="R557" s="5" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="S557" s="6">
         <v>46230.89233796296</v>
@@ -56342,7 +56351,7 @@
         <v>46180.77130787037</v>
       </c>
       <c r="E558" s="8" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="F558" s="6">
         <v>46234.541666666664</v>
@@ -56360,7 +56369,7 @@
         <v>1087</v>
       </c>
       <c r="K558" s="133" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="L558" s="102">
         <v>6.0</v>
@@ -56416,7 +56425,7 @@
         <v>46180.771319444444</v>
       </c>
       <c r="E559" s="8" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="F559" s="6">
         <v>46213.541666666664</v>
@@ -56434,7 +56443,7 @@
         <v>1087</v>
       </c>
       <c r="K559" s="133" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="L559" s="102">
         <v>1.0</v>
@@ -56446,7 +56455,7 @@
         <v>32</v>
       </c>
       <c r="O559" s="12" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="P559" s="64"/>
       <c r="Q559" s="115">
@@ -56490,7 +56499,7 @@
         <v>46180.77133101852</v>
       </c>
       <c r="E560" s="8" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="F560" s="6">
         <v>46176.541666666664</v>
@@ -56508,7 +56517,7 @@
         <v>1087</v>
       </c>
       <c r="K560" s="133" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="L560" s="102">
         <v>1.0</v>
@@ -56552,7 +56561,7 @@
         <v>46180.77134259259</v>
       </c>
       <c r="E561" s="8" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="F561" s="6">
         <v>46234.541666666664</v>
@@ -56570,7 +56579,7 @@
         <v>1087</v>
       </c>
       <c r="K561" s="133" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="L561" s="102">
         <v>1.0</v>
@@ -56582,7 +56591,7 @@
         <v>46209.91552083333</v>
       </c>
       <c r="O561" s="12" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="P561" s="6">
         <v>46232.76483796296</v>
@@ -56632,7 +56641,7 @@
         <v>46180.77135416667</v>
       </c>
       <c r="E562" s="8" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="F562" s="6">
         <v>46234.541666666664</v>
@@ -56650,7 +56659,7 @@
         <v>1087</v>
       </c>
       <c r="K562" s="133" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="L562" s="102">
         <v>1.0</v>
@@ -56662,7 +56671,7 @@
         <v>46209.91550925926</v>
       </c>
       <c r="O562" s="12" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="P562" s="6">
         <v>46213.74061342593</v>
@@ -56712,7 +56721,7 @@
         <v>46180.771365740744</v>
       </c>
       <c r="E563" s="8" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="F563" s="6">
         <v>46237.541666666664</v>
@@ -56724,13 +56733,13 @@
         <v>46231.71969907408</v>
       </c>
       <c r="I563" s="5" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="J563" s="14" t="s">
         <v>1087</v>
       </c>
       <c r="K563" s="133" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="L563" s="102">
         <v>1.0</v>
@@ -56747,7 +56756,7 @@
         <v>46175.0</v>
       </c>
       <c r="R563" s="5" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="S563" s="6">
         <v>46232.48646990741</v>
@@ -56786,7 +56795,7 @@
         <v>46180.77137731481</v>
       </c>
       <c r="E564" s="8" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="F564" s="6">
         <v>46230.541666666664</v>
@@ -56798,13 +56807,13 @@
         <v>46230.876284722224</v>
       </c>
       <c r="I564" s="5" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="J564" s="14" t="s">
         <v>1087</v>
       </c>
       <c r="K564" s="133" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="L564" s="102">
         <v>2.0</v>
@@ -56816,7 +56825,7 @@
         <v>46231.87368055555</v>
       </c>
       <c r="O564" s="5" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="P564" s="64"/>
       <c r="Q564" s="115">
@@ -56860,7 +56869,7 @@
         <v>46180.77138888889</v>
       </c>
       <c r="E565" s="8" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="F565" s="6">
         <v>46234.541666666664</v>
@@ -56878,7 +56887,7 @@
         <v>1087</v>
       </c>
       <c r="K565" s="133" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="L565" s="102">
         <v>1.0</v>
@@ -56890,7 +56899,7 @@
         <v>46230.58806712963</v>
       </c>
       <c r="O565" s="12" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="P565" s="6">
         <v>46230.879849537036</v>
@@ -56940,7 +56949,7 @@
         <v>46180.77140046296</v>
       </c>
       <c r="E566" s="8" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="F566" s="6">
         <v>46230.541666666664</v>
@@ -56958,7 +56967,7 @@
         <v>1087</v>
       </c>
       <c r="K566" s="133" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="L566" s="102">
         <v>4.0</v>
@@ -56970,7 +56979,7 @@
         <v>32</v>
       </c>
       <c r="O566" s="143" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="P566" s="64"/>
       <c r="Q566" s="115">
@@ -61483,6 +61492,7 @@
       <c r="Z726" s="144"/>
     </row>
   </sheetData>
+  <autoFilter ref="$A$1:$Z$566"/>
   <mergeCells count="2">
     <mergeCell ref="X436:Y436"/>
     <mergeCell ref="X441:Y441"/>
@@ -62311,177 +62321,178 @@
     <hyperlink r:id="rId821" ref="E449"/>
     <hyperlink r:id="rId822" ref="O449"/>
     <hyperlink r:id="rId823" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/microsite/ice-solution-2026" ref="Y449"/>
-    <hyperlink r:id="rId824" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/microsite/ice-solution-2026" ref="Y450"/>
-    <hyperlink r:id="rId825" ref="E451"/>
-    <hyperlink r:id="rId826" ref="O451"/>
-    <hyperlink r:id="rId827" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/microsite/ice-solution-2026" ref="Y451"/>
-    <hyperlink r:id="rId828" ref="E452"/>
-    <hyperlink r:id="rId829" ref="O452"/>
-    <hyperlink r:id="rId830" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/microsite/ice-solution-2026" ref="Y452"/>
-    <hyperlink r:id="rId831" ref="E453"/>
-    <hyperlink r:id="rId832" ref="O453"/>
-    <hyperlink r:id="rId833" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/microsite/ice-solution-2026" ref="Y453"/>
-    <hyperlink r:id="rId834" ref="E454"/>
-    <hyperlink r:id="rId835" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y454"/>
-    <hyperlink r:id="rId836" ref="E455"/>
-    <hyperlink r:id="rId837" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y455"/>
-    <hyperlink r:id="rId838" ref="O456"/>
-    <hyperlink r:id="rId839" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y456"/>
-    <hyperlink r:id="rId840" ref="O457"/>
-    <hyperlink r:id="rId841" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y457"/>
-    <hyperlink r:id="rId842" ref="O458"/>
-    <hyperlink r:id="rId843" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y458"/>
-    <hyperlink r:id="rId844" ref="O459"/>
-    <hyperlink r:id="rId845" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y459"/>
-    <hyperlink r:id="rId846" ref="E460"/>
-    <hyperlink r:id="rId847" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y460"/>
-    <hyperlink r:id="rId848" ref="E461"/>
-    <hyperlink r:id="rId849" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y461"/>
-    <hyperlink r:id="rId850" ref="E462"/>
-    <hyperlink r:id="rId851" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y462"/>
-    <hyperlink r:id="rId852" ref="E463"/>
-    <hyperlink r:id="rId853" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y463"/>
-    <hyperlink r:id="rId854" ref="O464"/>
-    <hyperlink r:id="rId855" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y464"/>
-    <hyperlink r:id="rId856" ref="O465"/>
-    <hyperlink r:id="rId857" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y465"/>
-    <hyperlink r:id="rId858" ref="O466"/>
-    <hyperlink r:id="rId859" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y466"/>
-    <hyperlink r:id="rId860" ref="O467"/>
-    <hyperlink r:id="rId861" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y467"/>
-    <hyperlink r:id="rId862" ref="E468"/>
-    <hyperlink r:id="rId863" ref="O468"/>
-    <hyperlink r:id="rId864" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y468"/>
-    <hyperlink r:id="rId865" ref="E469"/>
-    <hyperlink r:id="rId866" ref="O469"/>
-    <hyperlink r:id="rId867" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y469"/>
-    <hyperlink r:id="rId868" ref="O470"/>
-    <hyperlink r:id="rId869" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y470"/>
-    <hyperlink r:id="rId870" ref="O471"/>
-    <hyperlink r:id="rId871" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y471"/>
-    <hyperlink r:id="rId872" ref="E472"/>
-    <hyperlink r:id="rId873" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y472"/>
-    <hyperlink r:id="rId874" ref="E473"/>
-    <hyperlink r:id="rId875" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y473"/>
-    <hyperlink r:id="rId876" ref="O474"/>
-    <hyperlink r:id="rId877" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y474"/>
-    <hyperlink r:id="rId878" ref="O475"/>
-    <hyperlink r:id="rId879" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y475"/>
-    <hyperlink r:id="rId880" ref="O476"/>
-    <hyperlink r:id="rId881" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y476"/>
-    <hyperlink r:id="rId882" ref="O477"/>
-    <hyperlink r:id="rId883" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y477"/>
-    <hyperlink r:id="rId884" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y478"/>
-    <hyperlink r:id="rId885" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y479"/>
-    <hyperlink r:id="rId886" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y480"/>
-    <hyperlink r:id="rId887" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y481"/>
-    <hyperlink r:id="rId888" ref="E482"/>
-    <hyperlink r:id="rId889" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y482"/>
-    <hyperlink r:id="rId890" ref="E483"/>
-    <hyperlink r:id="rId891" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y483"/>
-    <hyperlink r:id="rId892" ref="E484"/>
-    <hyperlink r:id="rId893" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y484"/>
-    <hyperlink r:id="rId894" ref="E485"/>
-    <hyperlink r:id="rId895" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y485"/>
-    <hyperlink r:id="rId896" ref="E486"/>
-    <hyperlink r:id="rId897" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y486"/>
-    <hyperlink r:id="rId898" ref="E487"/>
-    <hyperlink r:id="rId899" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y487"/>
-    <hyperlink r:id="rId900" ref="E488"/>
-    <hyperlink r:id="rId901" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y488"/>
-    <hyperlink r:id="rId902" ref="E489"/>
-    <hyperlink r:id="rId903" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y489"/>
-    <hyperlink r:id="rId904" ref="E490"/>
-    <hyperlink r:id="rId905" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y490"/>
-    <hyperlink r:id="rId906" ref="E491"/>
-    <hyperlink r:id="rId907" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y491"/>
-    <hyperlink r:id="rId908" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y492"/>
-    <hyperlink r:id="rId909" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/microsite/reliable-microsite" ref="Y493"/>
-    <hyperlink r:id="rId910" ref="E494"/>
-    <hyperlink r:id="rId911" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y494"/>
-    <hyperlink r:id="rId912" ref="E495"/>
-    <hyperlink r:id="rId913" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y495"/>
-    <hyperlink r:id="rId914" ref="E496"/>
-    <hyperlink r:id="rId915" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y496"/>
-    <hyperlink r:id="rId916" ref="E497"/>
-    <hyperlink r:id="rId917" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y497"/>
-    <hyperlink r:id="rId918" ref="O498"/>
-    <hyperlink r:id="rId919" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y498"/>
-    <hyperlink r:id="rId920" ref="O499"/>
-    <hyperlink r:id="rId921" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y499"/>
-    <hyperlink r:id="rId922" ref="E500"/>
-    <hyperlink r:id="rId923" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y500"/>
-    <hyperlink r:id="rId924" ref="E501"/>
-    <hyperlink r:id="rId925" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y501"/>
-    <hyperlink r:id="rId926" ref="E502"/>
-    <hyperlink r:id="rId927" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y502"/>
-    <hyperlink r:id="rId928" ref="E503"/>
-    <hyperlink r:id="rId929" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y503"/>
-    <hyperlink r:id="rId930" ref="O504"/>
-    <hyperlink r:id="rId931" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y504"/>
-    <hyperlink r:id="rId932" ref="O505"/>
-    <hyperlink r:id="rId933" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y505"/>
-    <hyperlink r:id="rId934" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y506"/>
-    <hyperlink r:id="rId935" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y507"/>
-    <hyperlink r:id="rId936" ref="O508"/>
-    <hyperlink r:id="rId937" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y508"/>
-    <hyperlink r:id="rId938" ref="O509"/>
-    <hyperlink r:id="rId939" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y509"/>
-    <hyperlink r:id="rId940" ref="E510"/>
-    <hyperlink r:id="rId941" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y510"/>
-    <hyperlink r:id="rId942" ref="E511"/>
-    <hyperlink r:id="rId943" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y511"/>
-    <hyperlink r:id="rId944" ref="E512"/>
-    <hyperlink r:id="rId945" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y512"/>
-    <hyperlink r:id="rId946" ref="E513"/>
-    <hyperlink r:id="rId947" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y513"/>
-    <hyperlink r:id="rId948" ref="O514"/>
-    <hyperlink r:id="rId949" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y514"/>
-    <hyperlink r:id="rId950" ref="O515"/>
-    <hyperlink r:id="rId951" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y515"/>
-    <hyperlink r:id="rId952" ref="O516"/>
-    <hyperlink r:id="rId953" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y516"/>
-    <hyperlink r:id="rId954" ref="O517"/>
-    <hyperlink r:id="rId955" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y517"/>
-    <hyperlink r:id="rId956" ref="E518"/>
-    <hyperlink r:id="rId957" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y518"/>
-    <hyperlink r:id="rId958" ref="E519"/>
-    <hyperlink r:id="rId959" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y519"/>
-    <hyperlink r:id="rId960" ref="O520"/>
-    <hyperlink r:id="rId961" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y520"/>
-    <hyperlink r:id="rId962" ref="O521"/>
-    <hyperlink r:id="rId963" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y521"/>
-    <hyperlink r:id="rId964" ref="O522"/>
-    <hyperlink r:id="rId965" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/microsite/ice-solution-2026" ref="Y522"/>
-    <hyperlink r:id="rId966" ref="O523"/>
-    <hyperlink r:id="rId967" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/microsite/ice-solution-2026" ref="Y523"/>
-    <hyperlink r:id="rId968" ref="E524"/>
-    <hyperlink r:id="rId969" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y524"/>
-    <hyperlink r:id="rId970" ref="E525"/>
-    <hyperlink r:id="rId971" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y525"/>
-    <hyperlink r:id="rId972" ref="O526"/>
-    <hyperlink r:id="rId973" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/microsite/ice-solution-2026" ref="Y526"/>
-    <hyperlink r:id="rId974" ref="O527"/>
-    <hyperlink r:id="rId975" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/microsite/ice-solution-2026" ref="Y527"/>
-    <hyperlink r:id="rId976" ref="O528"/>
-    <hyperlink r:id="rId977" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y528"/>
-    <hyperlink r:id="rId978" ref="O529"/>
-    <hyperlink r:id="rId979" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y529"/>
-    <hyperlink r:id="rId980" ref="O530"/>
-    <hyperlink r:id="rId981" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/microsite/ice-solution-2026" ref="Y530"/>
-    <hyperlink r:id="rId982" ref="O531"/>
-    <hyperlink r:id="rId983" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/microsite/ice-solution-2026" ref="Y531"/>
-    <hyperlink r:id="rId984" ref="E532"/>
-    <hyperlink r:id="rId985" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y532"/>
-    <hyperlink r:id="rId986" ref="E533"/>
-    <hyperlink r:id="rId987" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y533"/>
-    <hyperlink r:id="rId988" ref="E543"/>
-    <hyperlink r:id="rId989" ref="O555"/>
-    <hyperlink r:id="rId990" ref="O559"/>
-    <hyperlink r:id="rId991" ref="O561"/>
-    <hyperlink r:id="rId992" ref="O562"/>
-    <hyperlink r:id="rId993" ref="O565"/>
+    <hyperlink r:id="rId824" ref="O450"/>
+    <hyperlink r:id="rId825" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/microsite/ice-solution-2026" ref="Y450"/>
+    <hyperlink r:id="rId826" ref="E451"/>
+    <hyperlink r:id="rId827" ref="O451"/>
+    <hyperlink r:id="rId828" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/microsite/ice-solution-2026" ref="Y451"/>
+    <hyperlink r:id="rId829" ref="E452"/>
+    <hyperlink r:id="rId830" ref="O452"/>
+    <hyperlink r:id="rId831" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/microsite/ice-solution-2026" ref="Y452"/>
+    <hyperlink r:id="rId832" ref="E453"/>
+    <hyperlink r:id="rId833" ref="O453"/>
+    <hyperlink r:id="rId834" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/microsite/ice-solution-2026" ref="Y453"/>
+    <hyperlink r:id="rId835" ref="E454"/>
+    <hyperlink r:id="rId836" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y454"/>
+    <hyperlink r:id="rId837" ref="E455"/>
+    <hyperlink r:id="rId838" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y455"/>
+    <hyperlink r:id="rId839" ref="O456"/>
+    <hyperlink r:id="rId840" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y456"/>
+    <hyperlink r:id="rId841" ref="O457"/>
+    <hyperlink r:id="rId842" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y457"/>
+    <hyperlink r:id="rId843" ref="O458"/>
+    <hyperlink r:id="rId844" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y458"/>
+    <hyperlink r:id="rId845" ref="O459"/>
+    <hyperlink r:id="rId846" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y459"/>
+    <hyperlink r:id="rId847" ref="E460"/>
+    <hyperlink r:id="rId848" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y460"/>
+    <hyperlink r:id="rId849" ref="E461"/>
+    <hyperlink r:id="rId850" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y461"/>
+    <hyperlink r:id="rId851" ref="E462"/>
+    <hyperlink r:id="rId852" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y462"/>
+    <hyperlink r:id="rId853" ref="E463"/>
+    <hyperlink r:id="rId854" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y463"/>
+    <hyperlink r:id="rId855" ref="O464"/>
+    <hyperlink r:id="rId856" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y464"/>
+    <hyperlink r:id="rId857" ref="O465"/>
+    <hyperlink r:id="rId858" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y465"/>
+    <hyperlink r:id="rId859" ref="O466"/>
+    <hyperlink r:id="rId860" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y466"/>
+    <hyperlink r:id="rId861" ref="O467"/>
+    <hyperlink r:id="rId862" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y467"/>
+    <hyperlink r:id="rId863" ref="E468"/>
+    <hyperlink r:id="rId864" ref="O468"/>
+    <hyperlink r:id="rId865" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y468"/>
+    <hyperlink r:id="rId866" ref="E469"/>
+    <hyperlink r:id="rId867" ref="O469"/>
+    <hyperlink r:id="rId868" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y469"/>
+    <hyperlink r:id="rId869" ref="O470"/>
+    <hyperlink r:id="rId870" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y470"/>
+    <hyperlink r:id="rId871" ref="O471"/>
+    <hyperlink r:id="rId872" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y471"/>
+    <hyperlink r:id="rId873" ref="E472"/>
+    <hyperlink r:id="rId874" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y472"/>
+    <hyperlink r:id="rId875" ref="E473"/>
+    <hyperlink r:id="rId876" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y473"/>
+    <hyperlink r:id="rId877" ref="O474"/>
+    <hyperlink r:id="rId878" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y474"/>
+    <hyperlink r:id="rId879" ref="O475"/>
+    <hyperlink r:id="rId880" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y475"/>
+    <hyperlink r:id="rId881" ref="O476"/>
+    <hyperlink r:id="rId882" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y476"/>
+    <hyperlink r:id="rId883" ref="O477"/>
+    <hyperlink r:id="rId884" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y477"/>
+    <hyperlink r:id="rId885" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y478"/>
+    <hyperlink r:id="rId886" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y479"/>
+    <hyperlink r:id="rId887" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y480"/>
+    <hyperlink r:id="rId888" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y481"/>
+    <hyperlink r:id="rId889" ref="E482"/>
+    <hyperlink r:id="rId890" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y482"/>
+    <hyperlink r:id="rId891" ref="E483"/>
+    <hyperlink r:id="rId892" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y483"/>
+    <hyperlink r:id="rId893" ref="E484"/>
+    <hyperlink r:id="rId894" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y484"/>
+    <hyperlink r:id="rId895" ref="E485"/>
+    <hyperlink r:id="rId896" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y485"/>
+    <hyperlink r:id="rId897" ref="E486"/>
+    <hyperlink r:id="rId898" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y486"/>
+    <hyperlink r:id="rId899" ref="E487"/>
+    <hyperlink r:id="rId900" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y487"/>
+    <hyperlink r:id="rId901" ref="E488"/>
+    <hyperlink r:id="rId902" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y488"/>
+    <hyperlink r:id="rId903" ref="E489"/>
+    <hyperlink r:id="rId904" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y489"/>
+    <hyperlink r:id="rId905" ref="E490"/>
+    <hyperlink r:id="rId906" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y490"/>
+    <hyperlink r:id="rId907" ref="E491"/>
+    <hyperlink r:id="rId908" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y491"/>
+    <hyperlink r:id="rId909" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y492"/>
+    <hyperlink r:id="rId910" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/microsite/reliable-microsite" ref="Y493"/>
+    <hyperlink r:id="rId911" ref="E494"/>
+    <hyperlink r:id="rId912" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y494"/>
+    <hyperlink r:id="rId913" ref="E495"/>
+    <hyperlink r:id="rId914" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y495"/>
+    <hyperlink r:id="rId915" ref="E496"/>
+    <hyperlink r:id="rId916" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y496"/>
+    <hyperlink r:id="rId917" ref="E497"/>
+    <hyperlink r:id="rId918" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y497"/>
+    <hyperlink r:id="rId919" ref="O498"/>
+    <hyperlink r:id="rId920" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y498"/>
+    <hyperlink r:id="rId921" ref="O499"/>
+    <hyperlink r:id="rId922" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y499"/>
+    <hyperlink r:id="rId923" ref="E500"/>
+    <hyperlink r:id="rId924" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y500"/>
+    <hyperlink r:id="rId925" ref="E501"/>
+    <hyperlink r:id="rId926" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y501"/>
+    <hyperlink r:id="rId927" ref="E502"/>
+    <hyperlink r:id="rId928" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y502"/>
+    <hyperlink r:id="rId929" ref="E503"/>
+    <hyperlink r:id="rId930" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y503"/>
+    <hyperlink r:id="rId931" ref="O504"/>
+    <hyperlink r:id="rId932" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y504"/>
+    <hyperlink r:id="rId933" ref="O505"/>
+    <hyperlink r:id="rId934" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y505"/>
+    <hyperlink r:id="rId935" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y506"/>
+    <hyperlink r:id="rId936" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y507"/>
+    <hyperlink r:id="rId937" ref="O508"/>
+    <hyperlink r:id="rId938" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y508"/>
+    <hyperlink r:id="rId939" ref="O509"/>
+    <hyperlink r:id="rId940" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y509"/>
+    <hyperlink r:id="rId941" ref="E510"/>
+    <hyperlink r:id="rId942" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y510"/>
+    <hyperlink r:id="rId943" ref="E511"/>
+    <hyperlink r:id="rId944" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y511"/>
+    <hyperlink r:id="rId945" ref="E512"/>
+    <hyperlink r:id="rId946" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y512"/>
+    <hyperlink r:id="rId947" ref="E513"/>
+    <hyperlink r:id="rId948" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y513"/>
+    <hyperlink r:id="rId949" ref="O514"/>
+    <hyperlink r:id="rId950" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y514"/>
+    <hyperlink r:id="rId951" ref="O515"/>
+    <hyperlink r:id="rId952" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y515"/>
+    <hyperlink r:id="rId953" ref="O516"/>
+    <hyperlink r:id="rId954" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y516"/>
+    <hyperlink r:id="rId955" ref="O517"/>
+    <hyperlink r:id="rId956" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y517"/>
+    <hyperlink r:id="rId957" ref="E518"/>
+    <hyperlink r:id="rId958" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y518"/>
+    <hyperlink r:id="rId959" ref="E519"/>
+    <hyperlink r:id="rId960" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y519"/>
+    <hyperlink r:id="rId961" ref="O520"/>
+    <hyperlink r:id="rId962" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y520"/>
+    <hyperlink r:id="rId963" ref="O521"/>
+    <hyperlink r:id="rId964" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y521"/>
+    <hyperlink r:id="rId965" ref="O522"/>
+    <hyperlink r:id="rId966" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/microsite/ice-solution-2026" ref="Y522"/>
+    <hyperlink r:id="rId967" ref="O523"/>
+    <hyperlink r:id="rId968" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/microsite/ice-solution-2026" ref="Y523"/>
+    <hyperlink r:id="rId969" ref="E524"/>
+    <hyperlink r:id="rId970" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y524"/>
+    <hyperlink r:id="rId971" ref="E525"/>
+    <hyperlink r:id="rId972" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y525"/>
+    <hyperlink r:id="rId973" ref="O526"/>
+    <hyperlink r:id="rId974" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/microsite/ice-solution-2026" ref="Y526"/>
+    <hyperlink r:id="rId975" ref="O527"/>
+    <hyperlink r:id="rId976" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/microsite/ice-solution-2026" ref="Y527"/>
+    <hyperlink r:id="rId977" ref="O528"/>
+    <hyperlink r:id="rId978" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y528"/>
+    <hyperlink r:id="rId979" ref="O529"/>
+    <hyperlink r:id="rId980" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y529"/>
+    <hyperlink r:id="rId981" ref="O530"/>
+    <hyperlink r:id="rId982" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/microsite/ice-solution-2026" ref="Y530"/>
+    <hyperlink r:id="rId983" ref="O531"/>
+    <hyperlink r:id="rId984" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/microsite/ice-solution-2026" ref="Y531"/>
+    <hyperlink r:id="rId985" ref="E532"/>
+    <hyperlink r:id="rId986" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y532"/>
+    <hyperlink r:id="rId987" ref="E533"/>
+    <hyperlink r:id="rId988" location="/aem/assets.html/content/dam/master-2/hs/lgcom/lgcom-common/guide" ref="Y533"/>
+    <hyperlink r:id="rId989" ref="E543"/>
+    <hyperlink r:id="rId990" ref="O555"/>
+    <hyperlink r:id="rId991" ref="O559"/>
+    <hyperlink r:id="rId992" ref="O561"/>
+    <hyperlink r:id="rId993" ref="O562"/>
+    <hyperlink r:id="rId994" ref="O565"/>
   </hyperlinks>
-  <drawing r:id="rId994"/>
+  <drawing r:id="rId995"/>
 </worksheet>
 </file>